--- a/reports/一级子公司B_现金流量表_2026-09.xlsx
+++ b/reports/一级子公司B_现金流量表_2026-09.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>50614200</v>
+        <v>49044160</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>439138440</v>
+        <v>426537598</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1068232</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>9236574</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>530041</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>4617632</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>267480</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2310704</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>211884</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1845961</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>160423</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1387038</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>106091</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>922750</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>80032</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>693540</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>53197</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>461464</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>132967</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1155443</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>67047</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>580110</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>42159</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>367129</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>162225</v>
+        <v>158221</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1407495</v>
+        <v>1366989</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>973350</v>
+        <v>940294</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>8444970</v>
+        <v>8193535</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>51749775</v>
+        <v>52862228</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>25956000</v>
+        <v>25204595</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>225199200</v>
+        <v>218820014</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>355405</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3077477</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>265409</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2309904</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>178165</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1539783</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>132453</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1154156</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>89169</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>770376</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>66570</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>579746</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>9192750</v>
+        <v>8960084</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>79758050</v>
+        <v>77518241</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3460800</v>
+        <v>3350795</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>30026560</v>
+        <v>29120733</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1946700</v>
+        <v>1892384</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>16889940</v>
+        <v>16413710</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>40556250</v>
+        <v>40495029</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>11193525</v>
+        <v>12367199</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>61800</v>
+        <v>60270</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>556200</v>
+        <v>540575</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>618000</v>
+        <v>601368</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>5562000</v>
+        <v>5405810</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>370800</v>
+        <v>359733</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3337200</v>
+        <v>3237046</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>679800</v>
+        <v>661638</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6180000</v>
+        <v>6014401</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>55620000</v>
+        <v>53982548</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>927000</v>
+        <v>896693</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>8343000</v>
+        <v>8099687</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4326000</v>
+        <v>4219170</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>38934000</v>
+        <v>37814989</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>144200</v>
+        <v>140447</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1297800</v>
+        <v>1261417</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6324200</v>
+        <v>6154848</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5644400</v>
+        <v>-5493210</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1236000</v>
+        <v>1196578</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>11124000</v>
+        <v>10802234</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2060000</v>
+        <v>1990490</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>18540000</v>
+        <v>17990886</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2060000</v>
+        <v>2009999</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>18540000</v>
+        <v>18014429</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>61800</v>
+        <v>59717</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>556200</v>
+        <v>539452</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3357800</v>
+        <v>3246785</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1648000</v>
+        <v>1595575</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>14832000</v>
+        <v>14384053</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>1648000</v>
+        <v>1602067</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>14832000</v>
+        <v>14414115</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>288400</v>
+        <v>280089</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2595600</v>
+        <v>2518107</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>247200</v>
+        <v>240785</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2224800</v>
+        <v>2159810</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>36050</v>
+        <v>34849</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>324450</v>
+        <v>314913</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>1972450</v>
+        <v>1910513</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1385350</v>
+        <v>1336272</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>6934475</v>
+        <v>8210261</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>6934475</v>
+        <v>8210261</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
